--- a/excel/10_leverage.xlsx
+++ b/excel/10_leverage.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\busi448\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\busi448\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E396A97-AA52-464F-99BC-89DED150795A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B83A9D94-073D-4440-A35D-205A5177D947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21600" xr2:uid="{85997A6B-105C-45C3-9CB4-DBADA1C8AA17}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{85997A6B-105C-45C3-9CB4-DBADA1C8AA17}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin" sheetId="1" r:id="rId1"/>
     <sheet name="Repo" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="haircut">Repo!$E$2</definedName>
-    <definedName name="init_cash">Repo!$C$3</definedName>
-    <definedName name="leverage">Repo!$C$13</definedName>
+    <definedName name="haircut">Repo!$C$4</definedName>
+    <definedName name="init_cash">Repo!$C$7</definedName>
+    <definedName name="leverage">Repo!$C$17</definedName>
     <definedName name="MV">Repo!$C$2</definedName>
-    <definedName name="repo_price">Repo!$C$4</definedName>
-    <definedName name="repo_rate">Repo!$E$3</definedName>
-    <definedName name="return">Repo!$C$17</definedName>
+    <definedName name="repo_price">Repo!$C$8</definedName>
+    <definedName name="repo_rate">Repo!$C$3</definedName>
+    <definedName name="return">Repo!$C$21</definedName>
     <definedName name="term">Repo!$C$5</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Assets</t>
   </si>
@@ -74,13 +74,7 @@
     <t>MV</t>
   </si>
   <si>
-    <t>Implied haircut</t>
-  </si>
-  <si>
     <t>Initial cash</t>
-  </si>
-  <si>
-    <t>Implied repo rate</t>
   </si>
   <si>
     <t>Repurchase price</t>
@@ -130,13 +124,23 @@
   </si>
   <si>
     <t>Percent margin (E/A)</t>
+  </si>
+  <si>
+    <t>Repo Rate</t>
+  </si>
+  <si>
+    <t>Haircut</t>
+  </si>
+  <si>
+    <t>Calculations</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -357,7 +361,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -409,14 +413,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -796,9 +802,9 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="28">
+        <v>21</v>
+      </c>
+      <c r="C7" s="27">
         <f>C5/E4</f>
         <v>1.5</v>
       </c>
@@ -809,7 +815,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="24">
         <f>E3/E4</f>
@@ -822,7 +828,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="12">
         <f>E4/C5</f>
@@ -832,10 +838,11 @@
         <f ca="1">_xlfn.FORMULATEXT(C9)</f>
         <v>=E4/C5</v>
       </c>
+      <c r="E9" s="27"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -848,10 +855,10 @@
     </row>
     <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C13" s="19">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -877,7 +884,7 @@
       </c>
       <c r="E15" s="16">
         <f>E3*(1+C13)</f>
-        <v>50000</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -888,7 +895,7 @@
       </c>
       <c r="E16" s="17">
         <f>C15-E15</f>
-        <v>115000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -905,11 +912,11 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="28">
+        <v>21</v>
+      </c>
+      <c r="C19" s="27">
         <f>C17/E16</f>
-        <v>1.4347826086956521</v>
+        <v>1.4473684210526316</v>
       </c>
       <c r="D19" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C19)</f>
@@ -918,11 +925,11 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C20" s="24">
         <f>E15/E16</f>
-        <v>0.43478260869565216</v>
+        <v>0.44736842105263158</v>
       </c>
       <c r="D20" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C20)</f>
@@ -931,11 +938,11 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="12">
         <f>E16/C17</f>
-        <v>0.69696969696969702</v>
+        <v>0.69090909090909092</v>
       </c>
       <c r="D21" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C21)</f>
@@ -944,11 +951,11 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="12">
         <f>E16/E4-1</f>
-        <v>0.14999999999999991</v>
+        <v>0.1399999999999999</v>
       </c>
       <c r="D22" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C22)</f>
@@ -956,12 +963,12 @@
       </c>
     </row>
     <row r="23" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B23" s="29" t="s">
-        <v>25</v>
+      <c r="B23" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="C23" s="12">
         <f>C12+C8*(C12-C13)</f>
-        <v>0.15000000000000002</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D23" t="str">
         <f ca="1">_xlfn.FORMULATEXT(C23)</f>
@@ -976,7 +983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8774C3A8-E238-4BA2-A94C-E40054297607}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
@@ -986,286 +993,306 @@
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>19576026.649999999</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="12">
-        <f>1-init_cash/MV</f>
-        <v>9.999999667961168E-3</v>
-      </c>
-      <c r="F2" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(haircut)</f>
-        <v>=1-init_cash/MV</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="30">
-        <v>19380266.390000001</v>
-      </c>
-      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="19">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="12">
-        <f>(repo_price/init_cash-1)*360/term</f>
-        <v>5.9999918298307975E-2</v>
-      </c>
-      <c r="F3" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(repo_rate)</f>
-        <v>=(repo_price/init_cash-1)*360/term</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="30">
-        <v>19383496.43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>13</v>
       </c>
       <c r="C5" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
+      <c r="E5" s="12"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="29">
+        <f>MV*(1-haircut)</f>
+        <v>19380266.383499999</v>
+      </c>
+      <c r="D7" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(init_cash)</f>
+        <v>=MV*(1-haircut)</v>
+      </c>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="29">
+        <f>init_cash*(1+repo_rate*term/360)</f>
+        <v>19383496.427897248</v>
+      </c>
+      <c r="D8" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(repo_price)</f>
+        <v>=init_cash*(1+repo_rate*term/360)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="30"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="30"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="10" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="13">
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="13">
         <f>MV</f>
         <v>19576026.649999999</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="16">
+        <f>init_cash</f>
+        <v>19380266.383499999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="5"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="17">
+        <f>C15-E13</f>
+        <v>195760.26649999991</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="6"/>
+      <c r="C15" s="15">
+        <f>SUM(C13:C14)</f>
+        <v>19576026.649999999</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="18">
+        <f>SUM(E13:E14)</f>
+        <v>19576026.649999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="21"/>
+      <c r="C16" s="13"/>
+      <c r="E16" s="22"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="24">
+        <f>E13/E14</f>
+        <v>99.000000000000043</v>
+      </c>
+      <c r="D17" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C17)</f>
+        <v>=E13/E14</v>
+      </c>
+      <c r="E17" s="22"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="31">
+        <f>E14/C15</f>
+        <v>9.9999999999999967E-3</v>
+      </c>
+      <c r="D18" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C18)</f>
+        <v>=E14/C15</v>
+      </c>
+      <c r="E18" s="22"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="21"/>
+      <c r="C19" s="13"/>
+      <c r="E19" s="22"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="16">
-        <f>init_cash</f>
-        <v>19380266.390000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="5"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="3" t="s">
+      <c r="C21" s="25">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="13">
+        <f>C13*(1+return)</f>
+        <v>19595602.676649995</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="16">
+        <f>repo_price</f>
+        <v>19383496.427897248</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="5"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="17">
-        <f>C11-E9</f>
-        <v>195760.25999999791</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="6"/>
-      <c r="C11" s="15">
-        <f>SUM(C9:C10)</f>
-        <v>19576026.649999999</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="18">
-        <f>SUM(E9:E10)</f>
-        <v>19576026.649999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="21"/>
-      <c r="C12" s="13"/>
-      <c r="E12" s="22"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="24">
-        <f>E9/E10</f>
-        <v>99.00000332038897</v>
-      </c>
-      <c r="D13" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C13)</f>
-        <v>=E9/E10</v>
-      </c>
-      <c r="E13" s="22"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="12">
-        <f>E10/C11</f>
-        <v>9.9999996679611142E-3</v>
-      </c>
-      <c r="D14" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C14)</f>
-        <v>=E10/C11</v>
-      </c>
-      <c r="E14" s="22"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="21"/>
-      <c r="C15" s="13"/>
-      <c r="E15" s="22"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="E24" s="17">
+        <f>C25-E23</f>
+        <v>212106.24875274673</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="6"/>
+      <c r="C25" s="15">
+        <f>SUM(C23:C24)</f>
+        <v>19595602.676649995</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="18">
+        <f>SUM(E23:E24)</f>
+        <v>19595602.676649995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="21"/>
+      <c r="C26" s="13"/>
+      <c r="E26" s="22"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="24">
+        <f>E23/E24</f>
+        <v>91.385786802031859</v>
+      </c>
+      <c r="D27" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C27)</f>
+        <v>=E23/E24</v>
+      </c>
+      <c r="E27" s="22"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="31">
+        <f>E24/C25</f>
+        <v>1.082417582417566E-2</v>
+      </c>
+      <c r="D28" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C28)</f>
+        <v>=E24/C25</v>
+      </c>
+      <c r="E28" s="22"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="23" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" t="s">
+      <c r="C29" s="31">
+        <f>E24/E14-1</f>
+        <v>8.3499999999983698E-2</v>
+      </c>
+      <c r="D29" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C29)</f>
+        <v>=E24/E14-1</v>
+      </c>
+      <c r="E29" s="22"/>
+    </row>
+    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="25">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="13">
-        <f>C9*(1+return)</f>
-        <v>19595602.676649995</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="16">
-        <f>repo_price</f>
-        <v>19383496.43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="5"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="17">
-        <f>C21-E19</f>
-        <v>212106.24664999545</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="6"/>
-      <c r="C21" s="15">
-        <f>SUM(C19:C20)</f>
-        <v>19595602.676649995</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="18">
-        <f>SUM(E19:E20)</f>
-        <v>19595602.676649995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="21"/>
-      <c r="C22" s="13"/>
-      <c r="E22" s="22"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="24">
-        <f>E19/E20</f>
-        <v>91.385787717914042</v>
-      </c>
-      <c r="D23" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C23)</f>
-        <v>=E19/E20</v>
-      </c>
-      <c r="E23" s="22"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="12">
-        <f>E20/C21</f>
-        <v>1.0824175716868356E-2</v>
-      </c>
-      <c r="D24" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C24)</f>
-        <v>=E20/C21</v>
-      </c>
-      <c r="E24" s="22"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="12">
-        <f>E20/E10-1</f>
-        <v>8.350002523493627E-2</v>
-      </c>
-      <c r="D25" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C25)</f>
-        <v>=E20/E10-1</v>
-      </c>
-      <c r="E25" s="22"/>
-    </row>
-    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="27">
+      <c r="C30" s="32">
         <f>return+leverage*(return-repo_rate*term/360)</f>
-        <v>8.3500025234956865E-2</v>
-      </c>
-      <c r="D26" t="str">
-        <f ca="1">_xlfn.FORMULATEXT(C26)</f>
+        <v>8.3500000000000046E-2</v>
+      </c>
+      <c r="D30" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C30)</f>
         <v>=return+leverage*(return-repo_rate*term/360)</v>
       </c>
-      <c r="E26" s="22"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="23"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="22"/>
+      <c r="E30" s="22"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="23"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
